--- a/Rent_results3.xlsx
+++ b/Rent_results3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Senior Thesis Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243F2F93-0484-4DA6-9531-C644F1ABA3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9397D266-F584-4ADB-9087-E34DE2E3A22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,15 +44,6 @@
   </si>
   <si>
     <t>const</t>
-  </si>
-  <si>
-    <t>event_-9</t>
-  </si>
-  <si>
-    <t>event_-8</t>
-  </si>
-  <si>
-    <t>event_-7</t>
   </si>
   <si>
     <t>event_-6</t>
@@ -98,6 +89,15 @@
   </si>
   <si>
     <t>event_9</t>
+  </si>
+  <si>
+    <t>event_10</t>
+  </si>
+  <si>
+    <t>event_11</t>
+  </si>
+  <si>
+    <t>event_12</t>
   </si>
   <si>
     <t>ratio_lag1</t>
@@ -254,58 +254,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>-3.1026533688254792E-3</c:v>
+                  <c:v>-6.742948251436379E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3.6530070461637848E-3</c:v>
+                  <c:v>-5.8665128114418191E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1776444604527599E-3</c:v>
+                  <c:v>-2.3746250280126391E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-9.7542723441124395E-3</c:v>
+                  <c:v>-1.766012913690732E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-5.3426765492221098E-3</c:v>
+                  <c:v>-1.4863637903747741E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-4.3341928794049731E-3</c:v>
+                  <c:v>6.6048719424210839E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-3.597163711983892E-3</c:v>
+                  <c:v>2.9851858512002119E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-9.3710815241023512E-4</c:v>
+                  <c:v>1.689208907639433E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.1456330355241359E-3</c:v>
+                  <c:v>3.7008142169069058E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.8293638220330074E-3</c:v>
+                  <c:v>6.4978161169015891E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.9733234984930325E-4</c:v>
+                  <c:v>1.1500558080319811E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.5169755654751731E-5</c:v>
+                  <c:v>-9.2200683926213049E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.9474525338108841E-4</c:v>
+                  <c:v>-4.0885997497725167E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.8114321293685507E-3</c:v>
+                  <c:v>1.8530490383941601E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-8.2458442031520252E-3</c:v>
+                  <c:v>-1.078112827049629E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1.7270166198272751E-3</c:v>
+                  <c:v>-6.7674683905256244E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-3.3484628271727782E-3</c:v>
+                  <c:v>1.1850003168736861E-5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-5.3275880233949521E-3</c:v>
+                  <c:v>1.580687892412627E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -313,7 +313,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-65BB-4784-9011-BB8889477044}"/>
+              <c16:uniqueId val="{00000000-BA9C-45BF-9CFA-5847BC0789F2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -326,11 +326,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1676736495"/>
-        <c:axId val="1676735535"/>
+        <c:axId val="70768992"/>
+        <c:axId val="70769472"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1676736495"/>
+        <c:axId val="70768992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -372,7 +372,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1676735535"/>
+        <c:crossAx val="70769472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -380,7 +380,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1676735535"/>
+        <c:axId val="70769472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -431,7 +431,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1676736495"/>
+        <c:crossAx val="70768992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1047,23 +1047,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>130175</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>434975</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1776049-5978-3E7F-8629-BD92B4E1F51B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED36CD0B-703B-D722-9A6D-151302EE4A79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1397,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>3.0080554949153459E-4</v>
+        <v>1.2648969034471181E-2</v>
       </c>
       <c r="C2">
-        <v>1.2748608030672781E-3</v>
+        <v>3.7231047654434669E-3</v>
       </c>
       <c r="D2">
-        <v>0.23595168097395819</v>
+        <v>3.3974249534620689</v>
       </c>
       <c r="E2">
-        <v>0.81347016458042898</v>
+        <v>6.8023242926026537E-4</v>
       </c>
       <c r="F2">
-        <v>-2.1978757098221409E-3</v>
+        <v>5.3518177835325366E-3</v>
       </c>
       <c r="G2">
-        <v>2.7994868088052111E-3</v>
+        <v>1.9946120285409819E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1420,22 +1420,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>-3.1026533688254792E-3</v>
+        <v>-6.742948251436379E-3</v>
       </c>
       <c r="C3">
-        <v>4.8274275465983339E-3</v>
+        <v>6.8346912448530887E-3</v>
       </c>
       <c r="D3">
-        <v>-0.64271360654843512</v>
+        <v>-0.98657686351438367</v>
       </c>
       <c r="E3">
-        <v>0.52040995041946914</v>
+        <v>0.3238501171003052</v>
       </c>
       <c r="F3">
-        <v>-1.256423749813477E-2</v>
+        <v>-2.013869693679966E-2</v>
       </c>
       <c r="G3">
-        <v>6.3589307604838084E-3</v>
+        <v>6.6528004339269026E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1443,22 +1443,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>-3.6530070461637848E-3</v>
+        <v>-5.8665128114418191E-3</v>
       </c>
       <c r="C4">
-        <v>2.676121793787011E-3</v>
+        <v>6.1016789658149776E-3</v>
       </c>
       <c r="D4">
-        <v>-1.3650376655669221</v>
+        <v>-0.96145877951123093</v>
       </c>
       <c r="E4">
-        <v>0.17224121199473821</v>
+        <v>0.3363215418243688</v>
       </c>
       <c r="F4">
-        <v>-8.8981093802290509E-3</v>
+        <v>-1.782558382966478E-2</v>
       </c>
       <c r="G4">
-        <v>1.5920952879014811E-3</v>
+        <v>6.0925582067811422E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1466,22 +1466,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>1.1776444604527599E-3</v>
+        <v>-2.3746250280126391E-3</v>
       </c>
       <c r="C5">
-        <v>5.2937560279827873E-3</v>
+        <v>2.795102851672743E-3</v>
       </c>
       <c r="D5">
-        <v>0.22245914889687629</v>
+        <v>-0.84956624282771331</v>
       </c>
       <c r="E5">
-        <v>0.82395647096656022</v>
+        <v>0.39556628657589171</v>
       </c>
       <c r="F5">
-        <v>-9.1979266973353149E-3</v>
+        <v>-7.8529259503764149E-3</v>
       </c>
       <c r="G5">
-        <v>1.155321561824083E-2</v>
+        <v>3.1036758943511372E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -1489,22 +1489,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>-9.7542723441124395E-3</v>
+        <v>-1.766012913690732E-3</v>
       </c>
       <c r="C6">
-        <v>2.375111551362111E-3</v>
+        <v>2.4076781621271909E-3</v>
       </c>
       <c r="D6">
-        <v>-4.106869144111748</v>
+        <v>-0.73349210100840634</v>
       </c>
       <c r="E6">
-        <v>4.0105828393194952E-5</v>
+        <v>0.46325834379865899</v>
       </c>
       <c r="F6">
-        <v>-1.440940544404723E-2</v>
+        <v>-6.4849753978236148E-3</v>
       </c>
       <c r="G6">
-        <v>-5.0991392441776476E-3</v>
+        <v>2.9529495704421521E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1512,22 +1512,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>-5.3426765492221098E-3</v>
+        <v>-1.4863637903747741E-4</v>
       </c>
       <c r="C7">
-        <v>1.9693653083223258E-3</v>
+        <v>1.938607801129256E-3</v>
       </c>
       <c r="D7">
-        <v>-2.7128925886144808</v>
+        <v>-7.6671712014619656E-2</v>
       </c>
       <c r="E7">
-        <v>6.6698722298575751E-3</v>
+        <v>0.93888470882112485</v>
       </c>
       <c r="F7">
-        <v>-9.2025616259364881E-3</v>
+        <v>-3.9482378493992058E-3</v>
       </c>
       <c r="G7">
-        <v>-1.482791472507732E-3</v>
+        <v>3.6509650913242511E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1535,22 +1535,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>-4.3341928794049731E-3</v>
+        <v>6.6048719424210839E-3</v>
       </c>
       <c r="C8">
-        <v>1.398788175545068E-3</v>
+        <v>4.4842029740662951E-3</v>
       </c>
       <c r="D8">
-        <v>-3.098534113441489</v>
+        <v>1.472919932621104</v>
       </c>
       <c r="E8">
-        <v>1.944805789716105E-3</v>
+        <v>0.14077262667248819</v>
       </c>
       <c r="F8">
-        <v>-7.0757673254737974E-3</v>
+        <v>-2.1840043861162529E-3</v>
       </c>
       <c r="G8">
-        <v>-1.59261843333615E-3</v>
+        <v>1.5393748270958419E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1558,22 +1558,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>-3.597163711983892E-3</v>
+        <v>2.9851858512002119E-3</v>
       </c>
       <c r="C9">
-        <v>1.1229141093072239E-3</v>
+        <v>4.5479036335094774E-3</v>
       </c>
       <c r="D9">
-        <v>-3.2034183934184801</v>
+        <v>0.65638722623870471</v>
       </c>
       <c r="E9">
-        <v>1.3580652292882621E-3</v>
+        <v>0.51157500720282045</v>
       </c>
       <c r="F9">
-        <v>-5.7980349239579246E-3</v>
+        <v>-5.9285414756372126E-3</v>
       </c>
       <c r="G9">
-        <v>-1.396292500009859E-3</v>
+        <v>1.1898913178037641E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1581,22 +1581,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>-9.3710815241023512E-4</v>
+        <v>1.689208907639433E-3</v>
       </c>
       <c r="C10">
-        <v>1.473852177677467E-3</v>
+        <v>7.0335304479857922E-3</v>
       </c>
       <c r="D10">
-        <v>-0.63582234813192284</v>
+        <v>0.24016515178706249</v>
       </c>
       <c r="E10">
-        <v>0.52489221953001597</v>
+        <v>0.81020222798893959</v>
       </c>
       <c r="F10">
-        <v>-3.8258053391939991E-3</v>
+        <v>-1.2096257454578589E-2</v>
       </c>
       <c r="G10">
-        <v>1.9515890343735291E-3</v>
+        <v>1.547467526985746E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1604,22 +1604,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>7.1456330355241359E-3</v>
+        <v>3.7008142169069058E-4</v>
       </c>
       <c r="C11">
-        <v>3.704103162630088E-3</v>
+        <v>2.568119722203584E-3</v>
       </c>
       <c r="D11">
-        <v>1.929112857226795</v>
+        <v>0.14410598481489059</v>
       </c>
       <c r="E11">
-        <v>5.3716853187809492E-2</v>
+        <v>0.88541677885423575</v>
       </c>
       <c r="F11">
-        <v>-1.142757582517466E-4</v>
+        <v>-4.663340741815342E-3</v>
       </c>
       <c r="G11">
-        <v>1.440554182930002E-2</v>
+        <v>5.4035035851967231E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1627,22 +1627,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>5.8293638220330074E-3</v>
+        <v>6.4978161169015891E-5</v>
       </c>
       <c r="C12">
-        <v>3.1518290472052931E-3</v>
+        <v>2.135702042525528E-3</v>
       </c>
       <c r="D12">
-        <v>1.849517767215791</v>
+        <v>3.0424731481821021E-2</v>
       </c>
       <c r="E12">
-        <v>6.4383084691107637E-2</v>
+        <v>0.97572832111288854</v>
       </c>
       <c r="F12">
-        <v>-3.481075959165603E-4</v>
+        <v>-4.1209209238896507E-3</v>
       </c>
       <c r="G12">
-        <v>1.2006835239982579E-2</v>
+        <v>4.2508772462276816E-3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1650,22 +1650,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>9.9733234984930325E-4</v>
+        <v>1.1500558080319811E-2</v>
       </c>
       <c r="C13">
-        <v>5.2799240155902592E-3</v>
+        <v>8.757946180748254E-3</v>
       </c>
       <c r="D13">
-        <v>0.18889142095689959</v>
+        <v>1.3131569711629849</v>
       </c>
       <c r="E13">
-        <v>0.85017791762280637</v>
+        <v>0.1891300598170392</v>
       </c>
       <c r="F13">
-        <v>-9.3511285618157053E-3</v>
+        <v>-5.6647010124868877E-3</v>
       </c>
       <c r="G13">
-        <v>1.134579326151431E-2</v>
+        <v>2.8665817173126499E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1673,22 +1673,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>4.5169755654751731E-5</v>
+        <v>-9.2200683926213049E-3</v>
       </c>
       <c r="C14">
-        <v>2.722716344416903E-3</v>
+        <v>5.5772191024770186E-3</v>
       </c>
       <c r="D14">
-        <v>1.6589960150411951E-2</v>
+        <v>-1.6531658920350429</v>
       </c>
       <c r="E14">
-        <v>0.98676373409690554</v>
+        <v>9.8297106014127E-2</v>
       </c>
       <c r="F14">
-        <v>-5.2912562195209321E-3</v>
+        <v>-2.015121696736507E-2</v>
       </c>
       <c r="G14">
-        <v>5.3815957308304364E-3</v>
+        <v>1.711080182122456E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1696,22 +1696,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>3.9474525338108841E-4</v>
+        <v>-4.0885997497725167E-3</v>
       </c>
       <c r="C15">
-        <v>1.9948493648026151E-3</v>
+        <v>6.1457919818822372E-3</v>
       </c>
       <c r="D15">
-        <v>0.19788223629614629</v>
+        <v>-0.66526816427007085</v>
       </c>
       <c r="E15">
-        <v>0.84313720274008574</v>
+        <v>0.50587898905400031</v>
       </c>
       <c r="F15">
-        <v>-3.5150876562146409E-3</v>
+        <v>-1.6134130690736739E-2</v>
       </c>
       <c r="G15">
-        <v>4.3045781629768177E-3</v>
+        <v>7.9569311911917087E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -1719,22 +1719,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>7.8114321293685507E-3</v>
+        <v>1.8530490383941601E-3</v>
       </c>
       <c r="C16">
-        <v>7.7623962641010496E-3</v>
+        <v>2.804739712637012E-3</v>
       </c>
       <c r="D16">
-        <v>1.0063171041002219</v>
+        <v>0.66068485073501759</v>
       </c>
       <c r="E16">
-        <v>0.31426305532314441</v>
+        <v>0.50881444106287499</v>
       </c>
       <c r="F16">
-        <v>-7.4025849819977733E-3</v>
+        <v>-3.644139784383603E-3</v>
       </c>
       <c r="G16">
-        <v>2.3025449240734869E-2</v>
+        <v>7.3502378611719236E-3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1742,22 +1742,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>-8.2458442031520252E-3</v>
+        <v>-1.078112827049629E-4</v>
       </c>
       <c r="C17">
-        <v>4.2591826159359379E-3</v>
+        <v>2.6364282487247488E-3</v>
       </c>
       <c r="D17">
-        <v>-1.9360156505851149</v>
+        <v>-4.0892932609530211E-2</v>
       </c>
       <c r="E17">
-        <v>5.2865784174199078E-2</v>
+        <v>0.96738125169694278</v>
       </c>
       <c r="F17">
-        <v>-1.6593688733965561E-2</v>
+        <v>-5.2751156980294792E-3</v>
       </c>
       <c r="G17">
-        <v>1.02000327661507E-4</v>
+        <v>5.0594931326195533E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1765,22 +1765,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>-1.7270166198272751E-3</v>
+        <v>-6.7674683905256244E-4</v>
       </c>
       <c r="C18">
-        <v>9.2048261353786637E-4</v>
+        <v>2.1300671865181258E-3</v>
       </c>
       <c r="D18">
-        <v>-1.876207757134601</v>
+        <v>-0.31771149911885821</v>
       </c>
       <c r="E18">
-        <v>6.0626757329968577E-2</v>
+        <v>0.75070378780267566</v>
       </c>
       <c r="F18">
-        <v>-3.531129390756795E-3</v>
+        <v>-4.8516018092786524E-3</v>
       </c>
       <c r="G18">
-        <v>7.7096151102243804E-5</v>
+        <v>3.4981081311735271E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1788,22 +1788,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>-3.3484628271727782E-3</v>
+        <v>1.1850003168736861E-5</v>
       </c>
       <c r="C19">
-        <v>7.2794984498829427E-4</v>
+        <v>2.5790395071052749E-3</v>
       </c>
       <c r="D19">
-        <v>-4.5998537539720514</v>
+        <v>4.5947350306538544E-3</v>
       </c>
       <c r="E19">
-        <v>4.2278765215891399E-6</v>
+        <v>0.99633394475744164</v>
       </c>
       <c r="F19">
-        <v>-4.7752183059013506E-3</v>
+        <v>-5.042974545463535E-3</v>
       </c>
       <c r="G19">
-        <v>-1.9217073484442059E-3</v>
+        <v>5.0666745518010087E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1811,22 +1811,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>-5.3275880233949521E-3</v>
+        <v>1.580687892412627E-3</v>
       </c>
       <c r="C20">
-        <v>4.7491935316714697E-4</v>
+        <v>2.8037718304163282E-3</v>
       </c>
       <c r="D20">
-        <v>-11.21787938913476</v>
+        <v>0.56377194294655331</v>
       </c>
       <c r="E20">
-        <v>3.3316375209372401E-29</v>
+        <v>0.57290934862168297</v>
       </c>
       <c r="F20">
-        <v>-6.2584128511636184E-3</v>
+        <v>-3.9146039160713204E-3</v>
       </c>
       <c r="G20">
-        <v>-4.3967631956262857E-3</v>
+        <v>7.0759797008965739E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1834,22 +1834,22 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.47757944567709071</v>
+        <v>0.49257179679686458</v>
       </c>
       <c r="C21">
-        <v>8.2271357974121939E-2</v>
+        <v>7.2366581878612418E-2</v>
       </c>
       <c r="D21">
-        <v>5.8049296551943508</v>
+        <v>6.8066196303578863</v>
       </c>
       <c r="E21">
-        <v>6.4393032818828997E-9</v>
+        <v>9.9918647676013175E-12</v>
       </c>
       <c r="F21">
-        <v>0.31633054708860953</v>
+        <v>0.35073590263051541</v>
       </c>
       <c r="G21">
-        <v>0.63882834426557178</v>
+        <v>0.63440769096321381</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1857,22 +1857,22 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>0.18156799953984379</v>
+        <v>0.42919866172012788</v>
       </c>
       <c r="C22">
-        <v>7.9183025743741933E-2</v>
+        <v>5.6286834925293378E-2</v>
       </c>
       <c r="D22">
-        <v>2.2930166893021728</v>
+        <v>7.6252051174982771</v>
       </c>
       <c r="E22">
-        <v>2.184704413177525E-2</v>
+        <v>2.436466586080122E-14</v>
       </c>
       <c r="F22">
-        <v>2.6372120895201721E-2</v>
+        <v>0.31887849246280159</v>
       </c>
       <c r="G22">
-        <v>0.33676387818448589</v>
+        <v>0.53951883097745412</v>
       </c>
     </row>
   </sheetData>
@@ -1911,22 +1911,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4.2718192551090321E-4</v>
+        <v>1.947181942838681E-2</v>
       </c>
       <c r="C2">
-        <v>1.7237574156523611E-3</v>
+        <v>6.0123107771368148E-3</v>
       </c>
       <c r="D2">
-        <v>0.24782021044952829</v>
+        <v>3.238658171569051</v>
       </c>
       <c r="E2">
-        <v>0.80427351693482652</v>
+        <v>1.2009341049515421E-3</v>
       </c>
       <c r="F2">
-        <v>-2.9513205272515648E-3</v>
+        <v>7.6879068413366336E-3</v>
       </c>
       <c r="G2">
-        <v>3.805684378273372E-3</v>
+        <v>3.1255732015436993E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1934,22 +1934,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>-3.9626386663212162E-3</v>
+        <v>-9.1170179028234148E-3</v>
       </c>
       <c r="C3">
-        <v>7.8493429804776405E-3</v>
+        <v>9.1828513976701751E-3</v>
       </c>
       <c r="D3">
-        <v>-0.50483698778061115</v>
+        <v>-0.99283082214926588</v>
       </c>
       <c r="E3">
-        <v>0.61367333456300477</v>
+        <v>0.32079240666992548</v>
       </c>
       <c r="F3">
-        <v>-1.934706821035968E-2</v>
+        <v>-2.7115075917640251E-2</v>
       </c>
       <c r="G3">
-        <v>1.142179087771724E-2</v>
+        <v>8.8810401119934247E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1957,22 +1957,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>-4.5157052860165222E-3</v>
+        <v>-8.9765308511720321E-3</v>
       </c>
       <c r="C4">
-        <v>4.0759065570688318E-3</v>
+        <v>7.6139278184485836E-3</v>
       </c>
       <c r="D4">
-        <v>-1.10790206369794</v>
+        <v>-1.1789619057619449</v>
       </c>
       <c r="E4">
-        <v>0.26790411425438881</v>
+        <v>0.23841334513354109</v>
       </c>
       <c r="F4">
-        <v>-1.2504335342222081E-2</v>
+        <v>-2.3899555156218881E-2</v>
       </c>
       <c r="G4">
-        <v>3.4729247701890389E-3</v>
+        <v>5.9464934538748168E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1980,22 +1980,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>1.191423924340186E-3</v>
+        <v>-4.070265169486862E-3</v>
       </c>
       <c r="C5">
-        <v>6.8344580220275836E-3</v>
+        <v>3.6267673951704432E-3</v>
       </c>
       <c r="D5">
-        <v>0.17432602856001239</v>
+        <v>-1.122284592860022</v>
       </c>
       <c r="E5">
-        <v>0.8616092445878496</v>
+        <v>0.26174145490205297</v>
       </c>
       <c r="F5">
-        <v>-1.2203867652684729E-2</v>
+        <v>-1.1178598644325081E-2</v>
       </c>
       <c r="G5">
-        <v>1.4586715501365109E-2</v>
+        <v>3.0380683053513519E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2003,22 +2003,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>-1.224514647945806E-2</v>
+        <v>-3.289952748339015E-3</v>
       </c>
       <c r="C6">
-        <v>3.3794721585247659E-3</v>
+        <v>3.4587304686258102E-3</v>
       </c>
       <c r="D6">
-        <v>-3.6233902529924689</v>
+        <v>-0.95120240740994988</v>
       </c>
       <c r="E6">
-        <v>2.9076660793016918E-4</v>
+        <v>0.34150163659579402</v>
       </c>
       <c r="F6">
-        <v>-1.886879019692244E-2</v>
+        <v>-1.006893989907694E-2</v>
       </c>
       <c r="G6">
-        <v>-5.6215027619936813E-3</v>
+        <v>3.4890344023989161E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -2026,22 +2026,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>-7.5424225834899803E-3</v>
+        <v>-6.9684607456684672E-4</v>
       </c>
       <c r="C7">
-        <v>2.7008480699066231E-3</v>
+        <v>2.5836223063887601E-3</v>
       </c>
       <c r="D7">
-        <v>-2.7926126861888778</v>
+        <v>-0.2697166969195503</v>
       </c>
       <c r="E7">
-        <v>5.2284253154024221E-3</v>
+        <v>0.78737821417076048</v>
       </c>
       <c r="F7">
-        <v>-1.2835987528221481E-2</v>
+        <v>-5.7606527447431246E-3</v>
       </c>
       <c r="G7">
-        <v>-2.2488576387584809E-3</v>
+        <v>4.366960595609432E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -2049,22 +2049,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>-5.791399979527611E-3</v>
+        <v>8.124778989717682E-3</v>
       </c>
       <c r="C8">
-        <v>2.080491657770842E-3</v>
+        <v>5.974922805026389E-3</v>
       </c>
       <c r="D8">
-        <v>-2.7836689264752201</v>
+        <v>1.3598132151402409</v>
       </c>
       <c r="E8">
-        <v>5.3747865792172804E-3</v>
+        <v>0.17388903939254641</v>
       </c>
       <c r="F8">
-        <v>-9.8690886988944924E-3</v>
+        <v>-3.5858545185410758E-3</v>
       </c>
       <c r="G8">
-        <v>-1.713711260160729E-3</v>
+        <v>1.9835412497976442E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -2072,22 +2072,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>-4.8930127222871732E-3</v>
+        <v>1.5466862921606689E-3</v>
       </c>
       <c r="C9">
-        <v>1.745806970035801E-3</v>
+        <v>5.8382909116873006E-3</v>
       </c>
       <c r="D9">
-        <v>-2.8027226413163162</v>
+        <v>0.26492107288872102</v>
       </c>
       <c r="E9">
-        <v>5.0673227173861886E-3</v>
+        <v>0.79107026434420868</v>
       </c>
       <c r="F9">
-        <v>-8.3147315075163403E-3</v>
+        <v>-9.896153626013959E-3</v>
       </c>
       <c r="G9">
-        <v>-1.471293937058007E-3</v>
+        <v>1.2989526210335301E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -2095,22 +2095,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>-7.2181632853077562E-4</v>
+        <v>2.1850351615079061E-3</v>
       </c>
       <c r="C10">
-        <v>2.0376474703043199E-3</v>
+        <v>7.5908246788503183E-3</v>
       </c>
       <c r="D10">
-        <v>-0.35424004350613858</v>
+        <v>0.28785214439162149</v>
       </c>
       <c r="E10">
-        <v>0.72315899633349434</v>
+        <v>0.77345992032428046</v>
       </c>
       <c r="F10">
-        <v>-4.7155319835163927E-3</v>
+        <v>-1.269270782199654E-2</v>
       </c>
       <c r="G10">
-        <v>3.271899326454841E-3</v>
+        <v>1.706277814501235E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -2118,22 +2118,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>1.1273126297876071E-2</v>
+        <v>-1.0998197997571649E-3</v>
       </c>
       <c r="C11">
-        <v>5.9017829600857778E-3</v>
+        <v>3.2914751099289178E-3</v>
       </c>
       <c r="D11">
-        <v>1.9101221400578621</v>
+        <v>-0.33414191601798759</v>
       </c>
       <c r="E11">
-        <v>5.6117488970509971E-2</v>
+        <v>0.73827247158097842</v>
       </c>
       <c r="F11">
-        <v>-2.9415574846424619E-4</v>
+        <v>-7.55099247122786E-3</v>
       </c>
       <c r="G11">
-        <v>2.2840408344216381E-2</v>
+        <v>5.3513528717135297E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -2141,22 +2141,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>5.6372657727416699E-3</v>
+        <v>-2.7182511481024661E-3</v>
       </c>
       <c r="C12">
-        <v>4.1422673377448267E-3</v>
+        <v>2.5373724978160158E-3</v>
       </c>
       <c r="D12">
-        <v>1.3609130732278529</v>
+        <v>-1.071285808623738</v>
       </c>
       <c r="E12">
-        <v>0.17354116162082139</v>
+        <v>0.28404093881629411</v>
       </c>
       <c r="F12">
-        <v>-2.4814290235748021E-3</v>
+        <v>-7.6914098591842946E-3</v>
       </c>
       <c r="G12">
-        <v>1.375596056905814E-2</v>
+        <v>2.2549075629793628E-3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -2164,22 +2164,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>3.5150714241185201E-3</v>
+        <v>1.5996887390844889E-2</v>
       </c>
       <c r="C13">
-        <v>6.111145893689867E-3</v>
+        <v>1.1543488354645011E-2</v>
       </c>
       <c r="D13">
-        <v>0.57519023195765073</v>
+        <v>1.3857931761509401</v>
       </c>
       <c r="E13">
-        <v>0.56516264827205653</v>
+        <v>0.16581006666355719</v>
       </c>
       <c r="F13">
-        <v>-8.462554431783462E-3</v>
+        <v>-6.6279340402168457E-3</v>
       </c>
       <c r="G13">
-        <v>1.54926972800205E-2</v>
+        <v>3.8621708821906631E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -2187,22 +2187,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>4.2328572901027378E-4</v>
+        <v>-1.173121434957076E-2</v>
       </c>
       <c r="C14">
-        <v>3.6747313444880601E-3</v>
+        <v>7.326099996568968E-3</v>
       </c>
       <c r="D14">
-        <v>0.11518821087293479</v>
+        <v>-1.601290503141485</v>
       </c>
       <c r="E14">
-        <v>0.9082959428368812</v>
+        <v>0.10931259146771601</v>
       </c>
       <c r="F14">
-        <v>-6.7790553590467741E-3</v>
+        <v>-2.609010648998495E-2</v>
       </c>
       <c r="G14">
-        <v>7.6256268170673217E-3</v>
+        <v>2.627677790843433E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -2210,22 +2210,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>-1.1682405463489119E-3</v>
+        <v>-5.9709238002377922E-3</v>
       </c>
       <c r="C15">
-        <v>2.5507543163236922E-3</v>
+        <v>7.6346703202279376E-3</v>
       </c>
       <c r="D15">
-        <v>-0.45799806703165918</v>
+        <v>-0.78208010952587226</v>
       </c>
       <c r="E15">
-        <v>0.64695382998983741</v>
+        <v>0.43416749538841742</v>
       </c>
       <c r="F15">
-        <v>-6.1676271397534373E-3</v>
+        <v>-2.0934602661721431E-2</v>
       </c>
       <c r="G15">
-        <v>3.831146047055613E-3</v>
+        <v>8.9927550612458485E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -2233,22 +2233,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>1.137209751112311E-2</v>
+        <v>1.1625682166345121E-3</v>
       </c>
       <c r="C16">
-        <v>1.012887161930494E-2</v>
+        <v>3.5243072987799439E-3</v>
       </c>
       <c r="D16">
-        <v>1.122740808507106</v>
+        <v>0.32987140963473111</v>
       </c>
       <c r="E16">
-        <v>0.26154759090327162</v>
+        <v>0.74149712723399053</v>
       </c>
       <c r="F16">
-        <v>-8.4801260667444721E-3</v>
+        <v>-5.7449471594258226E-3</v>
       </c>
       <c r="G16">
-        <v>3.1224321088990689E-2</v>
+        <v>8.0700835926948468E-3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -2256,22 +2256,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>-1.034997467865059E-2</v>
+        <v>-3.563288748359913E-4</v>
       </c>
       <c r="C17">
-        <v>5.5273996132628716E-3</v>
+        <v>3.3135286481078509E-3</v>
       </c>
       <c r="D17">
-        <v>-1.872485328148892</v>
+        <v>-0.10753758686814691</v>
       </c>
       <c r="E17">
-        <v>6.1139489849474427E-2</v>
+        <v>0.91436250818800346</v>
       </c>
       <c r="F17">
-        <v>-2.118347884880644E-2</v>
+        <v>-6.850725686869074E-3</v>
       </c>
       <c r="G17">
-        <v>4.8352949150526348E-4</v>
+        <v>6.1380679371970913E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -2279,22 +2279,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>-3.067964508060613E-3</v>
+        <v>-1.684520304289956E-3</v>
       </c>
       <c r="C18">
-        <v>1.718660478623231E-3</v>
+        <v>2.8451587874254959E-3</v>
       </c>
       <c r="D18">
-        <v>-1.785090508695627</v>
+        <v>-0.59206548039950746</v>
       </c>
       <c r="E18">
-        <v>7.4246637244262031E-2</v>
+        <v>0.55380674131450691</v>
       </c>
       <c r="F18">
-        <v>-6.4364771478145153E-3</v>
+        <v>-7.2609290579415797E-3</v>
       </c>
       <c r="G18">
-        <v>3.005481316932907E-4</v>
+        <v>3.8918884493616668E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -2302,22 +2302,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>-4.1883990981148034E-3</v>
+        <v>-9.9935581948391861E-4</v>
       </c>
       <c r="C19">
-        <v>1.424228352630795E-3</v>
+        <v>3.3270405268503878E-3</v>
       </c>
       <c r="D19">
-        <v>-2.9408199116230982</v>
+        <v>-0.30037380411172188</v>
       </c>
       <c r="E19">
-        <v>3.273447860941556E-3</v>
+        <v>0.76389204294831736</v>
       </c>
       <c r="F19">
-        <v>-6.9798353750319727E-3</v>
+        <v>-7.5202354272158461E-3</v>
       </c>
       <c r="G19">
-        <v>-1.3969628211976341E-3</v>
+        <v>5.5215237882480089E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -2325,22 +2325,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>-6.339238013527519E-3</v>
+        <v>3.9134924124245921E-4</v>
       </c>
       <c r="C20">
-        <v>1.7316731942775649E-3</v>
+        <v>3.757607177440747E-3</v>
       </c>
       <c r="D20">
-        <v>-3.6607588744088511</v>
+        <v>0.1041485239840854</v>
       </c>
       <c r="E20">
-        <v>2.5146933323709361E-4</v>
+        <v>0.91705148363341293</v>
       </c>
       <c r="F20">
-        <v>-9.7332551073049788E-3</v>
+        <v>-6.9734254945906134E-3</v>
       </c>
       <c r="G20">
-        <v>-2.9452209197500588E-3</v>
+        <v>7.7561239770755318E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -2348,22 +2348,22 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.49266893331563327</v>
+        <v>0.49842525282507588</v>
       </c>
       <c r="C21">
-        <v>7.3433480618552566E-2</v>
+        <v>7.9019980907788112E-2</v>
       </c>
       <c r="D21">
-        <v>6.7090505470492872</v>
+        <v>6.3075850829008706</v>
       </c>
       <c r="E21">
-        <v>1.9589480827747251E-11</v>
+        <v>2.8342278213605612E-10</v>
       </c>
       <c r="F21">
-        <v>0.34874195604385022</v>
+        <v>0.34354893618676852</v>
       </c>
       <c r="G21">
-        <v>0.63659591058741638</v>
+        <v>0.65330156946338325</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2371,22 +2371,22 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>0.16405365902268529</v>
+        <v>0.41041880255296409</v>
       </c>
       <c r="C22">
-        <v>6.5434372237003186E-2</v>
+        <v>5.8958498596369542E-2</v>
       </c>
       <c r="D22">
-        <v>2.5071480540606879</v>
+        <v>6.9611474566660076</v>
       </c>
       <c r="E22">
-        <v>1.217097200741396E-2</v>
+        <v>3.375122659465627E-12</v>
       </c>
       <c r="F22">
-        <v>3.5804646087171398E-2</v>
+        <v>0.29486226872152449</v>
       </c>
       <c r="G22">
-        <v>0.29230267195819909</v>
+        <v>0.52597533638440375</v>
       </c>
     </row>
   </sheetData>
@@ -2424,22 +2424,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>1.3265363847572581E-4</v>
+        <v>5.5651083178953186E-3</v>
       </c>
       <c r="C2">
-        <v>7.1013769967453902E-4</v>
+        <v>1.595851920859509E-3</v>
       </c>
       <c r="D2">
-        <v>0.18679988196165601</v>
+        <v>3.4872335240841221</v>
       </c>
       <c r="E2">
-        <v>0.85181753946871464</v>
+        <v>4.8804500876608838E-4</v>
       </c>
       <c r="F2">
-        <v>-1.2591906769504921E-3</v>
+        <v>2.4372960283516182E-3</v>
       </c>
       <c r="G2">
-        <v>1.524497953901943E-3</v>
+        <v>8.6929206074390208E-3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2447,22 +2447,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>-2.032814544378079E-3</v>
+        <v>-3.082798837089487E-3</v>
       </c>
       <c r="C3">
-        <v>1.858391462848412E-3</v>
+        <v>3.2020348967403299E-3</v>
       </c>
       <c r="D3">
-        <v>-1.0938570182959859</v>
+        <v>-0.96276241093679971</v>
       </c>
       <c r="E3">
-        <v>0.27401769226267991</v>
+        <v>0.33566676837511761</v>
       </c>
       <c r="F3">
-        <v>-5.6751948807376718E-3</v>
+        <v>-9.3586719119409644E-3</v>
       </c>
       <c r="G3">
-        <v>1.6095657919815141E-3</v>
+        <v>3.1930742377619908E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2470,22 +2470,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>-1.82205275749384E-3</v>
+        <v>-3.6515289647781161E-3</v>
       </c>
       <c r="C4">
-        <v>6.6123026394417095E-4</v>
+        <v>2.5500663955475649E-3</v>
       </c>
       <c r="D4">
-        <v>-2.7555495518693909</v>
+        <v>-1.4319348590898311</v>
       </c>
       <c r="E4">
-        <v>5.859362848610313E-3</v>
+        <v>0.15216246478926501</v>
       </c>
       <c r="F4">
-        <v>-3.118040260312328E-3</v>
+        <v>-8.649567258237215E-3</v>
       </c>
       <c r="G4">
-        <v>-5.2606525467535073E-4</v>
+        <v>1.3465093286809829E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -2493,22 +2493,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>1.1141332251219771E-3</v>
+        <v>-1.3391548304330131E-3</v>
       </c>
       <c r="C5">
-        <v>2.4107066581702868E-3</v>
+        <v>1.1871855301791941E-3</v>
       </c>
       <c r="D5">
-        <v>0.46216042974203991</v>
+        <v>-1.128008046249418</v>
       </c>
       <c r="E5">
-        <v>0.64396627748140789</v>
+        <v>0.25931652103481939</v>
       </c>
       <c r="F5">
-        <v>-3.6107650021826969E-3</v>
+        <v>-3.6659957125513231E-3</v>
       </c>
       <c r="G5">
-        <v>5.8390314524266514E-3</v>
+        <v>9.8768605168529731E-4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2516,22 +2516,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>-4.5853708323632739E-3</v>
+        <v>-2.3986010301791511E-4</v>
       </c>
       <c r="C6">
-        <v>1.5294025907338919E-3</v>
+        <v>1.115074487307805E-3</v>
       </c>
       <c r="D6">
-        <v>-2.9981450666713978</v>
+        <v>-0.2151067984678087</v>
       </c>
       <c r="E6">
-        <v>2.7162834524361431E-3</v>
+        <v>0.82968405356361408</v>
       </c>
       <c r="F6">
-        <v>-7.5829448280639537E-3</v>
+        <v>-2.4253659382206779E-3</v>
       </c>
       <c r="G6">
-        <v>-1.5877968366625941E-3</v>
+        <v>1.9456457321848481E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -2539,22 +2539,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>-2.9228282708684459E-3</v>
+        <v>6.0151564710901693E-4</v>
       </c>
       <c r="C7">
-        <v>6.9150121895039055E-4</v>
+        <v>9.6697233350715199E-4</v>
       </c>
       <c r="D7">
-        <v>-4.2267868671365783</v>
+        <v>0.62206086592710974</v>
       </c>
       <c r="E7">
-        <v>2.3705200487488059E-5</v>
+        <v>0.53390184633321613</v>
       </c>
       <c r="F7">
-        <v>-4.2781457552767584E-3</v>
+        <v>-1.2937153006116549E-3</v>
       </c>
       <c r="G7">
-        <v>-1.567510786460134E-3</v>
+        <v>2.4967465948296879E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -2562,22 +2562,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>-2.239918451641358E-3</v>
+        <v>2.0357409147643609E-3</v>
       </c>
       <c r="C8">
-        <v>7.4599654624505046E-4</v>
+        <v>1.6285845110166929E-3</v>
       </c>
       <c r="D8">
-        <v>-3.0025855520590738</v>
+        <v>1.2500063097698799</v>
       </c>
       <c r="E8">
-        <v>2.6769671914850879E-3</v>
+        <v>0.2112972423954054</v>
       </c>
       <c r="F8">
-        <v>-3.702044814872925E-3</v>
+        <v>-1.156226072608133E-3</v>
       </c>
       <c r="G8">
-        <v>-7.7779208840978971E-4</v>
+        <v>5.2277079021368546E-3</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -2585,22 +2585,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>-1.555793085558228E-3</v>
+        <v>1.3427395933171241E-3</v>
       </c>
       <c r="C9">
-        <v>7.1990061057879877E-4</v>
+        <v>1.881884988132348E-3</v>
       </c>
       <c r="D9">
-        <v>-2.1611220530947639</v>
+        <v>0.71350778702459827</v>
       </c>
       <c r="E9">
-        <v>3.0685912466836059E-2</v>
+        <v>0.47553159625972552</v>
       </c>
       <c r="F9">
-        <v>-2.966772354741068E-3</v>
+        <v>-2.345687206468865E-3</v>
       </c>
       <c r="G9">
-        <v>-1.4481381637538739E-4</v>
+        <v>5.0311663931031118E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -2608,22 +2608,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>8.6154476633377314E-5</v>
+        <v>8.6049922848512733E-4</v>
       </c>
       <c r="C10">
-        <v>8.4285632899396771E-4</v>
+        <v>2.8569634450063149E-3</v>
       </c>
       <c r="D10">
-        <v>0.1022172743677575</v>
+        <v>0.30119364319805819</v>
       </c>
       <c r="E10">
-        <v>0.9185842166101752</v>
+        <v>0.76326683689387975</v>
       </c>
       <c r="F10">
-        <v>-1.565813572336442E-3</v>
+        <v>-4.7390462288747293E-3</v>
       </c>
       <c r="G10">
-        <v>1.738122525603197E-3</v>
+        <v>6.460044685844984E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -2631,22 +2631,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>2.2222988819287429E-3</v>
+        <v>1.7663708183950509E-3</v>
       </c>
       <c r="C11">
-        <v>1.5728072576845821E-3</v>
+        <v>1.1139076983201399E-3</v>
       </c>
       <c r="D11">
-        <v>1.412950551360193</v>
+        <v>1.585742535991874</v>
       </c>
       <c r="E11">
-        <v>0.15767026395762671</v>
+        <v>0.1127977258464461</v>
       </c>
       <c r="F11">
-        <v>-8.6034669775624526E-4</v>
+        <v>-4.1684815241433158E-4</v>
       </c>
       <c r="G11">
-        <v>5.3049444616137314E-3</v>
+        <v>3.9495897892044343E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -2654,22 +2654,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>4.1852364769298551E-3</v>
+        <v>-5.8291052126588708E-4</v>
       </c>
       <c r="C12">
-        <v>2.6263773458348369E-3</v>
+        <v>9.6837550142387882E-4</v>
       </c>
       <c r="D12">
-        <v>1.5935396654129721</v>
+        <v>-0.60194678656036604</v>
       </c>
       <c r="E12">
-        <v>0.1110391773623538</v>
+        <v>0.54720955941536631</v>
       </c>
       <c r="F12">
-        <v>-9.6236853071832336E-4</v>
+        <v>-2.4808916275676049E-3</v>
       </c>
       <c r="G12">
-        <v>9.3328414845780337E-3</v>
+        <v>1.315070585035831E-3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -2677,22 +2677,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>-1.8157684743211749E-3</v>
+        <v>5.7866513651888517E-3</v>
       </c>
       <c r="C13">
-        <v>2.8704146253061978E-3</v>
+        <v>3.7864416785574791E-3</v>
       </c>
       <c r="D13">
-        <v>-0.63258055415164283</v>
+        <v>1.5282557758537541</v>
       </c>
       <c r="E13">
-        <v>0.52700758906753087</v>
+        <v>0.12644904539757609</v>
       </c>
       <c r="F13">
-        <v>-7.4416777606183572E-3</v>
+        <v>-1.6346379543451951E-3</v>
       </c>
       <c r="G13">
-        <v>3.8101408119760069E-3</v>
+        <v>1.32079406847229E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -2700,22 +2700,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>-4.969095240902905E-5</v>
+        <v>-4.3450294042420672E-3</v>
       </c>
       <c r="C14">
-        <v>1.007029109168676E-3</v>
+        <v>2.7918670320927199E-3</v>
       </c>
       <c r="D14">
-        <v>-4.9344107292042437E-2</v>
+        <v>-1.556316742271616</v>
       </c>
       <c r="E14">
-        <v>0.96064506977187614</v>
+        <v>0.1196327921792907</v>
       </c>
       <c r="F14">
-        <v>-2.023431737763088E-3</v>
+        <v>-9.8169882367685306E-3</v>
       </c>
       <c r="G14">
-        <v>1.9240498329450299E-3</v>
+        <v>1.1269294282843961E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -2723,22 +2723,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>-1.8438208313959211E-4</v>
+        <v>-3.0847535734515601E-3</v>
       </c>
       <c r="C15">
-        <v>1.136802055159951E-3</v>
+        <v>2.524176048757089E-3</v>
       </c>
       <c r="D15">
-        <v>-0.16219365746453471</v>
+        <v>-1.2220833705202541</v>
       </c>
       <c r="E15">
-        <v>0.87115335427992346</v>
+        <v>0.22167610105349381</v>
       </c>
       <c r="F15">
-        <v>-2.4124731688042111E-3</v>
+        <v>-8.0320477196540729E-3</v>
       </c>
       <c r="G15">
-        <v>2.043709002525027E-3</v>
+        <v>1.8625405727509549E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -2746,22 +2746,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>4.3092351237251671E-3</v>
+        <v>1.444208842516035E-4</v>
       </c>
       <c r="C16">
-        <v>3.3433021523726581E-3</v>
+        <v>1.0407935440908669E-3</v>
       </c>
       <c r="D16">
-        <v>1.288915846468442</v>
+        <v>0.13876035749026011</v>
       </c>
       <c r="E16">
-        <v>0.19742734435150239</v>
+        <v>0.8896395209965785</v>
       </c>
       <c r="F16">
-        <v>-2.2435166843604872E-3</v>
+        <v>-1.8954969775082961E-3</v>
       </c>
       <c r="G16">
-        <v>1.086198693181082E-2</v>
+        <v>2.1843387460115031E-3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -2769,22 +2769,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>-4.3260640925247458E-3</v>
+        <v>5.6447123184537318E-4</v>
       </c>
       <c r="C17">
-        <v>2.5484953555572941E-3</v>
+        <v>1.113119204065723E-3</v>
       </c>
       <c r="D17">
-        <v>-1.697497342143965</v>
+        <v>0.5071076213433513</v>
       </c>
       <c r="E17">
-        <v>8.9602673167791608E-2</v>
+        <v>0.61207930775847674</v>
       </c>
       <c r="F17">
-        <v>-9.3210232041846409E-3</v>
+        <v>-1.6172023186233351E-3</v>
       </c>
       <c r="G17">
-        <v>6.6889501913514927E-4</v>
+        <v>2.746144782314081E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -2792,22 +2792,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>-1.432358987556075E-3</v>
+        <v>-5.619685063014343E-4</v>
       </c>
       <c r="C18">
-        <v>9.5991466328329957E-4</v>
+        <v>1.344099677743592E-3</v>
       </c>
       <c r="D18">
-        <v>-1.492173254919164</v>
+        <v>-0.41810032068814962</v>
       </c>
       <c r="E18">
-        <v>0.1356537317465554</v>
+        <v>0.67587377051805375</v>
       </c>
       <c r="F18">
-        <v>-3.313757155823235E-3</v>
+        <v>-3.196355466310767E-3</v>
       </c>
       <c r="G18">
-        <v>4.4903918071108573E-4</v>
+        <v>2.072418453707898E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -2815,22 +2815,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>-2.0313221949383878E-3</v>
+        <v>8.6248035161219302E-4</v>
       </c>
       <c r="C19">
-        <v>9.8346812925778409E-4</v>
+        <v>1.4450742806822669E-3</v>
       </c>
       <c r="D19">
-        <v>-2.065468249053898</v>
+        <v>0.59684153482060986</v>
       </c>
       <c r="E19">
-        <v>3.8878716756396953E-2</v>
+        <v>0.55061318439584217</v>
       </c>
       <c r="F19">
-        <v>-3.9588843082266276E-3</v>
+        <v>-1.9698131935101748E-3</v>
       </c>
       <c r="G19">
-        <v>-1.037600816501489E-4</v>
+        <v>3.6947738967345609E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -2838,22 +2838,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>-2.105811529382461E-3</v>
+        <v>1.8192337901265061E-3</v>
       </c>
       <c r="C20">
-        <v>4.7640752691945358E-4</v>
+        <v>1.3574554777328891E-3</v>
       </c>
       <c r="D20">
-        <v>-4.4201894604794756</v>
+        <v>1.3401793428723281</v>
       </c>
       <c r="E20">
-        <v>9.8614404159423893E-6</v>
+        <v>0.18018704575367961</v>
       </c>
       <c r="F20">
-        <v>-3.0395531241083859E-3</v>
+        <v>-8.4133005684656993E-4</v>
       </c>
       <c r="G20">
-        <v>-1.172069934656536E-3</v>
+        <v>4.4797976370995821E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -2861,22 +2861,22 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.53309548602523282</v>
+        <v>0.48561793791059971</v>
       </c>
       <c r="C21">
-        <v>9.9760377374242981E-2</v>
+        <v>6.6377534693446219E-2</v>
       </c>
       <c r="D21">
-        <v>5.3437597176017917</v>
+        <v>7.3159984044804709</v>
       </c>
       <c r="E21">
-        <v>9.1038231383688258E-8</v>
+        <v>2.5547469768304611E-13</v>
       </c>
       <c r="F21">
-        <v>0.33756873928759212</v>
+        <v>0.35552036052888708</v>
       </c>
       <c r="G21">
-        <v>0.72862223276287352</v>
+        <v>0.61571551529231217</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2884,22 +2884,22 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>0.1669309003428224</v>
+        <v>0.43981030502256141</v>
       </c>
       <c r="C22">
-        <v>0.1039175983754296</v>
+        <v>5.5492398511534008E-2</v>
       </c>
       <c r="D22">
-        <v>1.6063775813961809</v>
+        <v>7.9255955197385726</v>
       </c>
       <c r="E22">
-        <v>0.1081909735928422</v>
+        <v>2.2705553621417992E-15</v>
       </c>
       <c r="F22">
-        <v>-3.6743849832917702E-2</v>
+        <v>0.3310472025242106</v>
       </c>
       <c r="G22">
-        <v>0.37060565051856248</v>
+        <v>0.54857340752091222</v>
       </c>
     </row>
   </sheetData>
@@ -2937,22 +2937,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>1.6409125823696E-4</v>
+        <v>5.370156578832024E-3</v>
       </c>
       <c r="C2">
-        <v>9.0770943196259127E-4</v>
+        <v>1.878445768641566E-3</v>
       </c>
       <c r="D2">
-        <v>0.18077509438474429</v>
+        <v>2.8588297136283871</v>
       </c>
       <c r="E2">
-        <v>0.8565441128082395</v>
+        <v>4.2520697122480867E-3</v>
       </c>
       <c r="F2">
-        <v>-1.6149865368370289E-3</v>
+        <v>1.6884705253828959E-3</v>
       </c>
       <c r="G2">
-        <v>1.9431690533109501E-3</v>
+        <v>9.051842632281152E-3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2960,22 +2960,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1.6657205008533151E-3</v>
+        <v>-3.3648564739574421E-3</v>
       </c>
       <c r="C3">
-        <v>4.4704668254539129E-4</v>
+        <v>6.0421757755779277E-3</v>
       </c>
       <c r="D3">
-        <v>3.726054942112639</v>
+        <v>-0.5568948337381987</v>
       </c>
       <c r="E3">
-        <v>1.945000262654764E-4</v>
+        <v>0.57759928460551935</v>
       </c>
       <c r="F3">
-        <v>7.8952510365623747E-4</v>
+        <v>-1.5207303382350551E-2</v>
       </c>
       <c r="G3">
-        <v>2.5419158980503928E-3</v>
+        <v>8.4775904344356647E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2983,22 +2983,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>-1.9173558164429819E-3</v>
+        <v>-3.0641201014223012E-3</v>
       </c>
       <c r="C4">
-        <v>9.335988396709402E-4</v>
+        <v>6.084194439827501E-3</v>
       </c>
       <c r="D4">
-        <v>-2.0537255778068242</v>
+        <v>-0.50361968732695117</v>
       </c>
       <c r="E4">
-        <v>4.0002259517919733E-2</v>
+        <v>0.614528655220135</v>
       </c>
       <c r="F4">
-        <v>-3.7471759182064091E-3</v>
+        <v>-1.4988922078423049E-2</v>
       </c>
       <c r="G4">
-        <v>-8.7535714679554599E-5</v>
+        <v>8.8606818755784505E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -3006,22 +3006,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>3.017938753300589E-3</v>
+        <v>1.520453209153312E-3</v>
       </c>
       <c r="C5">
-        <v>4.214557605354447E-3</v>
+        <v>2.8783276114986859E-3</v>
       </c>
       <c r="D5">
-        <v>0.71607486144367893</v>
+        <v>0.52824188708721864</v>
       </c>
       <c r="E5">
-        <v>0.47394512520582682</v>
+        <v>0.59733146024673667</v>
       </c>
       <c r="F5">
-        <v>-5.2424423639635008E-3</v>
+        <v>-4.1209652450913082E-3</v>
       </c>
       <c r="G5">
-        <v>1.127831987056468E-2</v>
+        <v>7.1618716633979332E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3029,22 +3029,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>-8.08852626367027E-3</v>
+        <v>2.535798181795348E-3</v>
       </c>
       <c r="C6">
-        <v>2.3457425133581972E-3</v>
+        <v>3.010994313266349E-3</v>
       </c>
       <c r="D6">
-        <v>-3.448173112610994</v>
+        <v>0.842179664910923</v>
       </c>
       <c r="E6">
-        <v>5.6439217790229363E-4</v>
+        <v>0.39968739446276819</v>
       </c>
       <c r="F6">
-        <v>-1.26860971068568E-2</v>
+        <v>-3.3656422298616079E-3</v>
       </c>
       <c r="G6">
-        <v>-3.4909554204837368E-3</v>
+        <v>8.4372385934523043E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -3052,22 +3052,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>-5.3565065420072416E-3</v>
+        <v>1.495991917286056E-3</v>
       </c>
       <c r="C7">
-        <v>1.545663501217818E-3</v>
+        <v>3.2126162016477789E-3</v>
       </c>
       <c r="D7">
-        <v>-3.4655062617360679</v>
+        <v>0.46566157405255859</v>
       </c>
       <c r="E7">
-        <v>5.2923420269869947E-4</v>
+        <v>0.6414577613425072</v>
       </c>
       <c r="F7">
-        <v>-8.3859513366122459E-3</v>
+        <v>-4.8006201340934571E-3</v>
       </c>
       <c r="G7">
-        <v>-2.3270617474022369E-3</v>
+        <v>7.79260396866557E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -3075,22 +3075,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>-4.0364921794889541E-3</v>
+        <v>5.5253774977336786E-3</v>
       </c>
       <c r="C8">
-        <v>1.083010648098434E-3</v>
+        <v>3.156603271495854E-3</v>
       </c>
       <c r="D8">
-        <v>-3.7271029482270439</v>
+        <v>1.750418732574939</v>
       </c>
       <c r="E8">
-        <v>1.9369335688231381E-4</v>
+        <v>8.0046085948843479E-2</v>
       </c>
       <c r="F8">
-        <v>-6.1591540446352669E-3</v>
+        <v>-6.614512278795056E-4</v>
       </c>
       <c r="G8">
-        <v>-1.9138303143426409E-3</v>
+        <v>1.1712206223346859E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -3098,22 +3098,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>-3.336005816197204E-3</v>
+        <v>7.1536484694995758E-3</v>
       </c>
       <c r="C9">
-        <v>9.5826296282867441E-4</v>
+        <v>4.9537535056427238E-3</v>
       </c>
       <c r="D9">
-        <v>-3.481305179895219</v>
+        <v>1.4440864813622629</v>
       </c>
       <c r="E9">
-        <v>4.9897662025955437E-4</v>
+        <v>0.1487146502795903</v>
       </c>
       <c r="F9">
-        <v>-5.2141667110600504E-3</v>
+        <v>-2.5555299898491991E-3</v>
       </c>
       <c r="G9">
-        <v>-1.457844921334358E-3</v>
+        <v>1.686282692884835E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -3121,22 +3121,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>-3.9198506338450588E-3</v>
+        <v>2.3248307727065242E-3</v>
       </c>
       <c r="C10">
-        <v>1.16908159127145E-3</v>
+        <v>1.220908206447415E-2</v>
       </c>
       <c r="D10">
-        <v>-3.3529316200950321</v>
+        <v>0.19041814613330271</v>
       </c>
       <c r="E10">
-        <v>7.9960458830823696E-4</v>
+        <v>0.84898147925200118</v>
       </c>
       <c r="F10">
-        <v>-6.2112084477258774E-3</v>
+        <v>-2.1604530357956741E-2</v>
       </c>
       <c r="G10">
-        <v>-1.628492819964242E-3</v>
+        <v>2.6254191903369788E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -3144,22 +3144,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>1.152218169648421E-4</v>
+        <v>7.1840157897343701E-3</v>
       </c>
       <c r="C11">
-        <v>1.097495655233986E-3</v>
+        <v>4.6144206577800693E-3</v>
       </c>
       <c r="D11">
-        <v>0.1049861258359851</v>
+        <v>1.5568619167006099</v>
       </c>
       <c r="E11">
-        <v>0.91638681785448595</v>
+        <v>0.1195032729587486</v>
       </c>
       <c r="F11">
-        <v>-2.0358301404829571E-3</v>
+        <v>-1.8600825090321919E-3</v>
       </c>
       <c r="G11">
-        <v>2.2662737744126422E-3</v>
+        <v>1.6228114088500931E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -3167,22 +3167,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>4.2841391995968106E-3</v>
+        <v>1.0722705590593431E-2</v>
       </c>
       <c r="C12">
-        <v>3.3959362530754209E-3</v>
+        <v>6.8036674220950449E-3</v>
       </c>
       <c r="D12">
-        <v>1.2615487689785161</v>
+        <v>1.5760184802348269</v>
       </c>
       <c r="E12">
-        <v>0.20711120073037059</v>
+        <v>0.1150215443253399</v>
       </c>
       <c r="F12">
-        <v>-2.3717735502249118E-3</v>
+        <v>-2.6122375195013268E-3</v>
       </c>
       <c r="G12">
-        <v>1.0940051949418529E-2</v>
+        <v>2.4057648700688199E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -3190,22 +3190,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>1.845455275075574E-4</v>
+        <v>7.628230613516529E-3</v>
       </c>
       <c r="C13">
-        <v>5.7752599607430993E-3</v>
+        <v>7.7940870943008674E-3</v>
       </c>
       <c r="D13">
-        <v>3.1954497072338203E-2</v>
+        <v>0.97872021716236468</v>
       </c>
       <c r="E13">
-        <v>0.97450833842452622</v>
+        <v>0.32771823989959342</v>
       </c>
       <c r="F13">
-        <v>-1.1134755996905121E-2</v>
+        <v>-7.6478993836816096E-3</v>
       </c>
       <c r="G13">
-        <v>1.150384705192024E-2</v>
+        <v>2.2904360610714668E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -3213,22 +3213,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>6.3467781384887311E-4</v>
+        <v>-1.0548349411445321E-2</v>
       </c>
       <c r="C14">
-        <v>3.5425081599828202E-3</v>
+        <v>5.9107585489286806E-3</v>
       </c>
       <c r="D14">
-        <v>0.1791605792241707</v>
+        <v>-1.784601641925839</v>
       </c>
       <c r="E14">
-        <v>0.85781161607341039</v>
+        <v>7.4325954912853306E-2</v>
       </c>
       <c r="F14">
-        <v>-6.3085105946567108E-3</v>
+        <v>-2.2133223288657761E-2</v>
       </c>
       <c r="G14">
-        <v>7.5778662223544568E-3</v>
+        <v>1.036524465767128E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -3236,22 +3236,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>6.5288318022997784E-3</v>
+        <v>-4.4897094090460476E-3</v>
       </c>
       <c r="C15">
-        <v>5.2258133900355804E-3</v>
+        <v>6.9734612032741356E-3</v>
       </c>
       <c r="D15">
-        <v>1.2493426984493461</v>
+        <v>-0.64382797554506621</v>
       </c>
       <c r="E15">
-        <v>0.21153975703838951</v>
+        <v>0.51968699065983959</v>
       </c>
       <c r="F15">
-        <v>-3.713574232097127E-3</v>
+        <v>-1.8157442215050699E-2</v>
       </c>
       <c r="G15">
-        <v>1.6771237836696679E-2</v>
+        <v>9.1780233969586053E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -3259,22 +3259,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>4.4477163045085737E-3</v>
+        <v>3.010729384684766E-3</v>
       </c>
       <c r="C16">
-        <v>6.8314387274218003E-3</v>
+        <v>2.9457737462097902E-3</v>
       </c>
       <c r="D16">
-        <v>0.65106582697656012</v>
+        <v>1.0220504506018331</v>
       </c>
       <c r="E16">
-        <v>0.51500399485980397</v>
+        <v>0.30675702293465168</v>
       </c>
       <c r="F16">
-        <v>-8.9416575638302936E-3</v>
+        <v>-2.762881064490057E-3</v>
       </c>
       <c r="G16">
-        <v>1.7837090172847441E-2</v>
+        <v>8.7843398338595877E-3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -3282,22 +3282,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>-7.4970841223117677E-3</v>
+        <v>3.267431501177739E-3</v>
       </c>
       <c r="C17">
-        <v>3.6567524159820011E-3</v>
+        <v>3.0639784220048969E-3</v>
       </c>
       <c r="D17">
-        <v>-2.050202821920736</v>
+        <v>1.0664016031286909</v>
       </c>
       <c r="E17">
-        <v>4.0344642743770143E-2</v>
+        <v>0.28624213731824788</v>
       </c>
       <c r="F17">
-        <v>-1.4664187158016319E-2</v>
+        <v>-2.737855855359727E-3</v>
       </c>
       <c r="G17">
-        <v>-3.2998108660721529E-4</v>
+        <v>9.2727188577152054E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -3305,22 +3305,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>-2.1644183316932609E-3</v>
+        <v>3.9534336014956373E-3</v>
       </c>
       <c r="C18">
-        <v>2.4727844565193011E-3</v>
+        <v>2.5793214889055891E-3</v>
       </c>
       <c r="D18">
-        <v>-0.8752959951632433</v>
+        <v>1.532741699125334</v>
       </c>
       <c r="E18">
-        <v>0.38141287263440238</v>
+        <v>0.12533951050457209</v>
       </c>
       <c r="F18">
-        <v>-7.0109868080015418E-3</v>
+        <v>-1.101943621309545E-3</v>
       </c>
       <c r="G18">
-        <v>2.6821501446150199E-3</v>
+        <v>9.0088108243008194E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -3328,22 +3328,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>-2.240822629942762E-3</v>
+        <v>5.5704782217625148E-3</v>
       </c>
       <c r="C19">
-        <v>4.0479067182028752E-3</v>
+        <v>3.208672309547197E-3</v>
       </c>
       <c r="D19">
-        <v>-0.55357565920827501</v>
+        <v>1.736069527943978</v>
       </c>
       <c r="E19">
-        <v>0.57986928806800764</v>
+        <v>8.2551541574581125E-2</v>
       </c>
       <c r="F19">
-        <v>-1.017457401039812E-2</v>
+        <v>-7.1840394314094582E-4</v>
       </c>
       <c r="G19">
-        <v>5.6929287505125999E-3</v>
+        <v>1.185936038666598E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -3351,22 +3351,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>-2.9570487356700508E-3</v>
+        <v>4.4997255230565421E-3</v>
       </c>
       <c r="C20">
-        <v>3.5213423404863199E-3</v>
+        <v>3.1299571216113781E-3</v>
       </c>
       <c r="D20">
-        <v>-0.83975042746388129</v>
+        <v>1.437631682551604</v>
       </c>
       <c r="E20">
-        <v>0.40104833341994589</v>
+        <v>0.15053858650013349</v>
       </c>
       <c r="F20">
-        <v>-9.8587529002592197E-3</v>
+        <v>-1.634877708456413E-3</v>
       </c>
       <c r="G20">
-        <v>3.9446554289191164E-3</v>
+        <v>1.0634328754569501E-2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -3374,22 +3374,22 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.27676938957067548</v>
+        <v>0.46681960432439651</v>
       </c>
       <c r="C21">
-        <v>0.1114939823737062</v>
+        <v>5.6062127358343213E-2</v>
       </c>
       <c r="D21">
-        <v>2.482370650668825</v>
+        <v>8.3268264391847779</v>
       </c>
       <c r="E21">
-        <v>1.305114415869325E-2</v>
+        <v>8.3038348396177953E-17</v>
       </c>
       <c r="F21">
-        <v>5.8245199625267842E-2</v>
+        <v>0.3569398538053461</v>
       </c>
       <c r="G21">
-        <v>0.49529357951608322</v>
+        <v>0.57669935484344681</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -3397,22 +3397,22 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>0.24509757767686829</v>
+        <v>0.50657083662271041</v>
       </c>
       <c r="C22">
-        <v>4.0985167726207347E-2</v>
+        <v>5.1510593572573461E-2</v>
       </c>
       <c r="D22">
-        <v>5.980153096217399</v>
+        <v>9.8343040040686187</v>
       </c>
       <c r="E22">
-        <v>2.229279998867232E-9</v>
+        <v>8.0119664895325381E-23</v>
       </c>
       <c r="F22">
-        <v>0.16476812503316851</v>
+        <v>0.40561192839818611</v>
       </c>
       <c r="G22">
-        <v>0.32542703032056808</v>
+        <v>0.60752974484723477</v>
       </c>
     </row>
   </sheetData>
